--- a/Excel/10. Vlookup_&_Xlookup/10_VlookUP_&_XlookuP..xlsx
+++ b/Excel/10. Vlookup_&_Xlookup/10_VlookUP_&_XlookuP..xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Weekend\Excel\10. Vlookup_&amp;_Xlookup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A291E2-1CC9-4F57-A063-E47161211BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CD3D88-119C-42A0-8741-CBD4613CDC8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="2" xr2:uid="{B82847AD-2FF7-4D5D-85F7-A04A8A77E089}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="26">
   <si>
     <t>Student ID</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>XlookUp</t>
+  </si>
+  <si>
+    <t>Xlookup</t>
   </si>
 </sst>
 </file>
@@ -213,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -230,6 +233,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1028,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D60197-C7FB-4AEB-B782-500F0AC33394}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -1040,12 +1047,12 @@
     <col min="8" max="8" width="42.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1070,8 +1077,11 @@
       <c r="H2" s="7" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1100,8 +1110,12 @@
         <f>_xlfn.XLOOKUP(A3,$C$13:$C$18,$B$13:$B$18,,0)</f>
         <v>Introduction to Data Science and Machine Learning</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3" t="str">
+        <f>_xlfn.XLOOKUP(A3,$A$13:$A$18,$B$13:$B$18,"Null",0)</f>
+        <v>Introduction to Data Science and Machine Learning</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1114,7 +1128,7 @@
       <c r="D4" s="4">
         <v>9</v>
       </c>
-      <c r="E4" t="e">
+      <c r="E4" s="8" t="e">
         <f t="shared" ref="E4:E7" si="0">VLOOKUP(A4,$B$13:$C$18,2,0)</f>
         <v>#N/A</v>
       </c>
@@ -1130,8 +1144,12 @@
         <f t="shared" ref="H4:H7" si="3">_xlfn.XLOOKUP(A4,$C$13:$C$18,$B$13:$B$18,,0)</f>
         <v>Full-Stack Web Development Bootcamp</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4" t="str">
+        <f t="shared" ref="I4:I7" si="4">_xlfn.XLOOKUP(A4,$A$13:$A$18,$B$13:$B$18,"Null",0)</f>
+        <v>Full-Stack Web Development Bootcamp</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -1160,8 +1178,12 @@
         <f t="shared" si="3"/>
         <v>Cybersecurity Essentials: Protecting Digital Assets</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5" t="str">
+        <f t="shared" si="4"/>
+        <v>Cybersecurity Essentials: Protecting Digital Assets</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1190,8 +1212,12 @@
         <f t="shared" si="3"/>
         <v>Advanced Excel and Data Analysis</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6" t="str">
+        <f t="shared" si="4"/>
+        <v>Advanced Excel and Data Analysis</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
@@ -1220,13 +1246,17 @@
         <f t="shared" si="3"/>
         <v>Cloud Computing with AWS and Azure</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7" t="str">
+        <f t="shared" si="4"/>
+        <v>Cloud Computing with AWS and Azure</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
@@ -1237,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -1248,7 +1278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>6</v>
       </c>
@@ -1259,7 +1289,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>8</v>
       </c>
